--- a/www/flightdata/xlsx/eoss-336.xlsx
+++ b/www/flightdata/xlsx/eoss-336.xlsx
@@ -3654,7 +3654,7 @@
         <v>32826.96</v>
       </c>
       <c r="I2">
-        <v>640</v>
+        <v>472</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
